--- a/NECP Scenario/Results/Regional Results/EL52_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL52_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547329769348572E-12</v>
+        <v>2.284571093697724E-12</v>
       </c>
       <c r="C2">
-        <v>8.102418582286559E-13</v>
+        <v>1.196288511768661E-12</v>
       </c>
       <c r="D2">
-        <v>1.190481067941039E-12</v>
+        <v>1.757700543281431E-12</v>
       </c>
       <c r="E2">
-        <v>1.749248247040148E-12</v>
+        <v>2.582700595704692E-12</v>
       </c>
       <c r="F2">
-        <v>2.570244866102058E-12</v>
+        <v>3.79487131149417E-12</v>
       </c>
       <c r="G2">
-        <v>3.776475183882454E-12</v>
+        <v>5.575831136720244E-12</v>
       </c>
       <c r="H2">
-        <v>2.288776150709157E-11</v>
+        <v>3.379307855830926E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.441022183194332E-08</v>
+        <v>8.027581879086E-08</v>
       </c>
       <c r="C3">
-        <v>4.835627650562441E-08</v>
+        <v>7.195201542333513E-08</v>
       </c>
       <c r="D3">
-        <v>1.372531047263702E-07</v>
+        <v>1.996953852143898E-07</v>
       </c>
       <c r="E3">
-        <v>2.83615336280774E-07</v>
+        <v>3.937803839022642E-07</v>
       </c>
       <c r="F3">
-        <v>3.724122311894997E-06</v>
+        <v>4.154554159031094E-06</v>
       </c>
       <c r="G3">
-        <v>1.667618444099386</v>
+        <v>1.285280774371225</v>
       </c>
       <c r="H3">
-        <v>1.899452578650492</v>
+        <v>1.671478771716751</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.62486885596705E-08</v>
+        <v>6.823444597436463E-08</v>
       </c>
       <c r="C4">
-        <v>4.110283503424468E-08</v>
+        <v>6.115921311252931E-08</v>
       </c>
       <c r="D4">
-        <v>1.166651390219009E-07</v>
+        <v>1.6974107743494E-07</v>
       </c>
       <c r="E4">
-        <v>2.410730358433995E-07</v>
+        <v>3.347133263198383E-07</v>
       </c>
       <c r="F4">
-        <v>3.165503965115851E-06</v>
+        <v>3.531371035179621E-06</v>
       </c>
       <c r="G4">
-        <v>1.417475677482366</v>
+        <v>1.092488658215101</v>
       </c>
       <c r="H4">
-        <v>1.614534691852679</v>
+        <v>1.420756955959134</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.000599318404893</v>
+        <v>1.001770669442786</v>
       </c>
       <c r="D5">
-        <v>0.9901019025859874</v>
+        <v>0.9889640832806211</v>
       </c>
       <c r="E5">
-        <v>1.167558549274371</v>
+        <v>1.168254565180801</v>
       </c>
       <c r="F5">
-        <v>1.271795547106634</v>
+        <v>1.274885796375017</v>
       </c>
       <c r="G5">
-        <v>1.355671241300319</v>
+        <v>1.357005851150323</v>
       </c>
       <c r="H5">
-        <v>1.427425466191527</v>
+        <v>1.433124674758819</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.7138596952447108</v>
+        <v>0.7091255755718041</v>
       </c>
       <c r="C7">
-        <v>3.565125002235119</v>
+        <v>3.565125001994603</v>
       </c>
       <c r="D7">
-        <v>3.45118421840001</v>
+        <v>3.44439380349271</v>
       </c>
       <c r="E7">
-        <v>3.928277780794516</v>
+        <v>3.928277780483724</v>
       </c>
       <c r="F7">
-        <v>4.148527780757617</v>
+        <v>4.148527780762202</v>
       </c>
       <c r="G7">
-        <v>4.348972225215586</v>
+        <v>4.348972225102755</v>
       </c>
       <c r="H7">
-        <v>4.549416661752205</v>
+        <v>4.549416661282705</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.2496012920363011</v>
+        <v>0.2479460054339035</v>
       </c>
       <c r="C9">
-        <v>0.245947885169985</v>
+        <v>0.2447765340461975</v>
       </c>
       <c r="D9">
-        <v>0.216605866079743</v>
+        <v>0.2153694144358157</v>
       </c>
       <c r="E9">
-        <v>0.2059651502958847</v>
+        <v>0.2052691342768544</v>
       </c>
       <c r="F9">
-        <v>0.1787386419573453</v>
+        <v>0.1756483926847749</v>
       </c>
       <c r="G9">
-        <v>0.1649484178481531</v>
+        <v>0.1636138079502113</v>
       </c>
       <c r="H9">
-        <v>0.1632796601872832</v>
+        <v>0.1575804514043797</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>8.600874320500891E-08</v>
+        <v>1.275170127797249E-07</v>
       </c>
       <c r="D10">
-        <v>9.47302158099244E-08</v>
+        <v>1.46264970676288E-07</v>
       </c>
       <c r="E10">
-        <v>1.133785410439251E-07</v>
+        <v>1.708673492032263E-07</v>
       </c>
       <c r="F10">
-        <v>9.319217624343397E-08</v>
+        <v>1.395479706577744E-07</v>
       </c>
       <c r="G10">
-        <v>8.531248329334538E-08</v>
+        <v>1.279182097693032E-07</v>
       </c>
       <c r="H10">
-        <v>4.026046033739512E-07</v>
+        <v>6.083455988558203E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -771,16 +771,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.111417286464745</v>
+        <v>1.121263604863529</v>
       </c>
       <c r="C11">
-        <v>1.317580391307307</v>
+        <v>1.293224566540865</v>
       </c>
       <c r="D11">
-        <v>1.258759502123819</v>
+        <v>1.249827824026059</v>
       </c>
       <c r="E11">
-        <v>1.213508420589804</v>
+        <v>1.198406327884276</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>8.344469783595958</v>
+        <v>8.344469785972313</v>
       </c>
       <c r="C14">
-        <v>8.4772579823517</v>
+        <v>8.477257980836358</v>
       </c>
       <c r="D14">
-        <v>9.322379894454468</v>
+        <v>9.322379883354872</v>
       </c>
       <c r="E14">
-        <v>11.13555049427964</v>
+        <v>11.13555039203226</v>
       </c>
       <c r="F14">
-        <v>11.30112275556848</v>
+        <v>11.30112277162105</v>
       </c>
       <c r="G14">
-        <v>13.79963690236802</v>
+        <v>13.79963692802855</v>
       </c>
       <c r="H14">
-        <v>17.82461986088665</v>
+        <v>17.82462002289188</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -953,25 +953,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.4440702503579835</v>
+        <v>0.4320352411203461</v>
       </c>
       <c r="C18">
-        <v>0.5708021838256697</v>
+        <v>0.5656481188133761</v>
       </c>
       <c r="D18">
-        <v>0.9035796620643283</v>
+        <v>0.8961887608399066</v>
       </c>
       <c r="E18">
-        <v>0.8998993574804817</v>
+        <v>0.8857691749271905</v>
       </c>
       <c r="F18">
-        <v>0.9190073130916405</v>
+        <v>0.9191940175801244</v>
       </c>
       <c r="G18">
-        <v>0.9511276057474715</v>
+        <v>0.9536400109271878</v>
       </c>
       <c r="H18">
-        <v>0.956097606997694</v>
+        <v>0.958165821490176</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.6022921909599E-08</v>
+        <v>6.835772835198448E-08</v>
       </c>
       <c r="C19">
-        <v>4.420432349276507E-08</v>
+        <v>6.640396165864956E-08</v>
       </c>
       <c r="D19">
-        <v>1.007219597437323E-07</v>
+        <v>1.471284527631638E-07</v>
       </c>
       <c r="E19">
-        <v>2.213690324114153E-07</v>
+        <v>3.140308231921627E-07</v>
       </c>
       <c r="F19">
-        <v>1.321693023928685E-06</v>
+        <v>1.728439523399885E-06</v>
       </c>
       <c r="G19">
-        <v>3.126639740404599E-06</v>
+        <v>4.551628254130867E-06</v>
       </c>
       <c r="H19">
-        <v>5.047122339073745E-06</v>
+        <v>8.179352722237718E-06</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1005,25 +1005,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.355256200285301</v>
+        <v>0.3456281928958898</v>
       </c>
       <c r="C20">
-        <v>0.4566417470566832</v>
+        <v>0.4525184950541904</v>
       </c>
       <c r="D20">
-        <v>0.7228637296489915</v>
+        <v>0.7169510086760579</v>
       </c>
       <c r="E20">
-        <v>0.7199194859859778</v>
+        <v>0.7086153399422058</v>
       </c>
       <c r="F20">
-        <v>0.7352058504758804</v>
+        <v>0.7353552140638822</v>
       </c>
       <c r="G20">
-        <v>0.7609020846044535</v>
+        <v>0.7629120087408232</v>
       </c>
       <c r="H20">
-        <v>0.7648780855979607</v>
+        <v>0.7665326571932468</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.681833753159498E-08</v>
+        <v>5.468618268497652E-08</v>
       </c>
       <c r="C21">
-        <v>3.536345879421209E-08</v>
+        <v>5.31231693269197E-08</v>
       </c>
       <c r="D21">
-        <v>8.057756779498582E-08</v>
+        <v>1.17702762210531E-07</v>
       </c>
       <c r="E21">
-        <v>1.770952259291324E-07</v>
+        <v>2.512246585537302E-07</v>
       </c>
       <c r="F21">
-        <v>1.057354419142949E-06</v>
+        <v>1.382751618719908E-06</v>
       </c>
       <c r="G21">
-        <v>2.50131179232368E-06</v>
+        <v>3.641302603304695E-06</v>
       </c>
       <c r="H21">
-        <v>4.037697871258995E-06</v>
+        <v>6.543482177790177E-06</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.369049598198618E-08</v>
+        <v>2.106964635135186E-08</v>
       </c>
       <c r="D22">
-        <v>2.101063087586936E-08</v>
+        <v>3.241847567696109E-08</v>
       </c>
       <c r="E22">
-        <v>6.232868251227335E-08</v>
+        <v>1.014479273504336E-07</v>
       </c>
       <c r="F22">
-        <v>0.1468295616230197</v>
+        <v>0.1468295614871745</v>
       </c>
       <c r="G22">
-        <v>0.1468295616946158</v>
+        <v>0.1468295615701778</v>
       </c>
       <c r="H22">
-        <v>0.1468295606814669</v>
+        <v>0.1468295600812589</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.2408219163058115</v>
+        <v>0.2408219161819177</v>
       </c>
       <c r="C23">
-        <v>0.2408219164144255</v>
+        <v>0.2408219163416026</v>
       </c>
       <c r="D23">
-        <v>0.2408219163414253</v>
+        <v>0.2408219162349362</v>
       </c>
       <c r="E23">
-        <v>0.2408219162811275</v>
+        <v>0.2408219161446676</v>
       </c>
       <c r="F23">
-        <v>0.2408219161879162</v>
+        <v>0.2408219160055486</v>
       </c>
       <c r="G23">
-        <v>0.2408219160030877</v>
+        <v>0.2408219157324299</v>
       </c>
       <c r="H23">
-        <v>0.2408219127860271</v>
+        <v>0.2408219110312389</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.111692851482531</v>
+        <v>2.130400859876502</v>
       </c>
       <c r="C24">
-        <v>2.503402894244541</v>
+        <v>2.457126899879986</v>
       </c>
       <c r="D24">
-        <v>2.39164321955906</v>
+        <v>2.374673120753317</v>
       </c>
       <c r="E24">
-        <v>2.305666197117322</v>
+        <v>2.276972321084665</v>
       </c>
       <c r="F24">
-        <v>1.654287215674123E-07</v>
+        <v>2.474627317080955E-07</v>
       </c>
       <c r="G24">
-        <v>1.546529759814447E-07</v>
+        <v>2.315781835360493E-07</v>
       </c>
       <c r="H24">
-        <v>7.37924061468555E-07</v>
+        <v>1.112416580092444E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.577965007577494E-09</v>
+        <v>3.807428711908972E-09</v>
       </c>
       <c r="C25">
-        <v>2.249142284645417E-09</v>
+        <v>3.308340813745015E-09</v>
       </c>
       <c r="D25">
-        <v>2.624263683961459E-09</v>
+        <v>3.885539098328527E-09</v>
       </c>
       <c r="E25">
-        <v>3.506457954635435E-09</v>
+        <v>5.182329470163478E-09</v>
       </c>
       <c r="F25">
-        <v>4.174157743183302E-09</v>
+        <v>6.15955198521367E-09</v>
       </c>
       <c r="G25">
-        <v>4.965029158214506E-09</v>
+        <v>7.333835871345947E-09</v>
       </c>
       <c r="H25">
-        <v>2.77475983674176E-08</v>
+        <v>4.099657408093336E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.229593234466097E-08</v>
+        <v>1.813609227692642E-08</v>
       </c>
       <c r="D27">
-        <v>5.449919283511932E-08</v>
+        <v>8.306710397965369E-08</v>
       </c>
       <c r="E27">
-        <v>4.342337914906501E-07</v>
+        <v>7.005802854097861E-07</v>
       </c>
       <c r="F27">
-        <v>2.300021365838264</v>
+        <v>1.852466170222231</v>
       </c>
       <c r="G27">
-        <v>5.312031668416691</v>
+        <v>5.355567615813748</v>
       </c>
       <c r="H27">
-        <v>8.150879305066885</v>
+        <v>8.43949909769993</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>3.585757649910432E-07</v>
+        <v>1.527901611197397E-07</v>
       </c>
       <c r="D30">
-        <v>0.3679083230491944</v>
+        <v>0.2385249363500812</v>
       </c>
       <c r="E30">
-        <v>0.9830012586010116</v>
+        <v>0.7120194925110878</v>
       </c>
       <c r="F30">
-        <v>2.277357088698278</v>
+        <v>1.692998298441382</v>
       </c>
       <c r="G30">
-        <v>4.643156748468352</v>
+        <v>3.894375573809249</v>
       </c>
       <c r="H30">
-        <v>5.887902983384147</v>
+        <v>5.459592204383654</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>1.32065835797605</v>
+        <v>1.317927462267942</v>
       </c>
       <c r="C31">
-        <v>1.321351877601532</v>
+        <v>1.319268833260943</v>
       </c>
       <c r="D31">
-        <v>1.316487672176486</v>
+        <v>1.314803345274656</v>
       </c>
       <c r="E31">
-        <v>1.313508108008178</v>
+        <v>1.312296855190972</v>
       </c>
       <c r="F31">
-        <v>1.309101832786283</v>
+        <v>1.310031523762612</v>
       </c>
       <c r="G31">
-        <v>1.294661426356612</v>
+        <v>1.301423297305247</v>
       </c>
       <c r="H31">
-        <v>1.301565026131355</v>
+        <v>1.300680355078423</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>7.166163192788559E-09</v>
+        <v>1.071578031758643E-08</v>
       </c>
       <c r="D32">
-        <v>2.492297310565974E-08</v>
+        <v>3.982199998642174E-08</v>
       </c>
       <c r="E32">
-        <v>1.023227617811867E-07</v>
+        <v>2.100363028358065E-07</v>
       </c>
       <c r="F32">
-        <v>2.186507881031792</v>
+        <v>2.186507567709977</v>
       </c>
       <c r="G32">
-        <v>2.19170475258501</v>
+        <v>2.191704740660044</v>
       </c>
       <c r="H32">
-        <v>2.192394067477442</v>
+        <v>2.192393985969089</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.0968880911608096</v>
+        <v>0.09688808874342804</v>
       </c>
       <c r="C33">
-        <v>0.09688809248166996</v>
+        <v>0.09688809057683952</v>
       </c>
       <c r="D33">
-        <v>0.09688808745279724</v>
+        <v>0.09688808359397126</v>
       </c>
       <c r="E33">
-        <v>0.09688808423153873</v>
+        <v>0.09688807880858864</v>
       </c>
       <c r="F33">
-        <v>0.09578358356840516</v>
+        <v>0.09578388088182521</v>
       </c>
       <c r="G33">
-        <v>0.09670663421430407</v>
+        <v>0.0967066205452629</v>
       </c>
       <c r="H33">
-        <v>0.09688790011001149</v>
+        <v>0.09688781983438756</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>1.512232106198415E-08</v>
+        <v>2.249293850818862E-08</v>
       </c>
       <c r="D34">
-        <v>1.839285801215828E-08</v>
+        <v>2.781593236993046E-08</v>
       </c>
       <c r="E34">
-        <v>3.493653965372704E-08</v>
+        <v>5.283215731137255E-08</v>
       </c>
       <c r="F34">
-        <v>5.854851552232606E-08</v>
+        <v>8.746930066440247E-08</v>
       </c>
       <c r="G34">
-        <v>7.755146374753919E-08</v>
+        <v>1.169650594764837E-07</v>
       </c>
       <c r="H34">
-        <v>3.917704103184739E-07</v>
+        <v>5.997254717166829E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.1229455513496367</v>
+        <v>0.1229455513401044</v>
       </c>
       <c r="C35">
-        <v>0.122945548859803</v>
+        <v>0.122945547647175</v>
       </c>
       <c r="D35">
-        <v>0.1229455474022814</v>
+        <v>0.1229455452918744</v>
       </c>
       <c r="E35">
-        <v>0.1229455439850708</v>
+        <v>0.1229452392420581</v>
       </c>
       <c r="F35">
-        <v>0.1229455344981406</v>
+        <v>0.1229451927697082</v>
       </c>
       <c r="G35">
-        <v>0.122945008461655</v>
+        <v>0.1229448490061569</v>
       </c>
       <c r="H35">
-        <v>0.122945138739821</v>
+        <v>0.1229447962463833</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>4.712239948103342E-07</v>
+        <v>7.579099707816129E-07</v>
       </c>
       <c r="D36">
-        <v>4.52005012403127E-07</v>
+        <v>7.283106487120569E-07</v>
       </c>
       <c r="E36">
-        <v>1.464976133324882</v>
+        <v>1.212906355183553</v>
       </c>
       <c r="F36">
-        <v>1.510494268872438</v>
+        <v>1.24801015298414</v>
       </c>
       <c r="G36">
-        <v>1.530836291029774</v>
+        <v>1.28390372887151</v>
       </c>
       <c r="H36">
-        <v>1.571429588540987</v>
+        <v>1.299767815243787</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.3530239441400079</v>
+        <v>0.3519978601422105</v>
       </c>
       <c r="C37">
-        <v>0.3462641675619188</v>
+        <v>0.3448229147421882</v>
       </c>
       <c r="D37">
-        <v>0.3302373348226635</v>
+        <v>0.3273639550681336</v>
       </c>
       <c r="E37">
-        <v>0.319816903728513</v>
+        <v>0.3178431572653544</v>
       </c>
       <c r="F37">
-        <v>0.3294730784516739</v>
+        <v>0.3278606681334277</v>
       </c>
       <c r="G37">
-        <v>0.3335243814586299</v>
+        <v>0.3374072578621642</v>
       </c>
       <c r="H37">
-        <v>0.3438646590401366</v>
+        <v>0.3419962573203855</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.005729887721626166</v>
+        <v>0.009486869854444602</v>
       </c>
       <c r="C38">
-        <v>0.01179619806436999</v>
+        <v>0.01532051008201275</v>
       </c>
       <c r="D38">
-        <v>0.03708406545421407</v>
+        <v>0.04139718246291065</v>
       </c>
       <c r="E38">
-        <v>0.2101992013991392</v>
+        <v>0.1931766160940502</v>
       </c>
       <c r="F38">
-        <v>0.9014539482442986</v>
+        <v>0.7599525497144937</v>
       </c>
       <c r="G38">
-        <v>2.032968160804062</v>
+        <v>2.157498409494598</v>
       </c>
       <c r="H38">
-        <v>2.793582495657373</v>
+        <v>3.308272537199932</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0.4440703507911273</v>
+        <v>0.4320353897538932</v>
       </c>
       <c r="C40">
-        <v>0.5708022763862698</v>
+        <v>0.5656482571693532</v>
       </c>
       <c r="D40">
-        <v>0.9035799000393928</v>
+        <v>0.8961891076637446</v>
       </c>
       <c r="E40">
-        <v>0.8998998624648504</v>
+        <v>0.8857698827383976</v>
       </c>
       <c r="F40">
-        <v>0.9190123589069763</v>
+        <v>0.9191999005738068</v>
       </c>
       <c r="G40">
-        <v>2.618749176486598</v>
+        <v>2.238925336926667</v>
       </c>
       <c r="H40">
-        <v>2.855555232770525</v>
+        <v>2.629652772559649</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0.3552562833523271</v>
+        <v>0.3456283158165185</v>
       </c>
       <c r="C41">
-        <v>0.456641823522977</v>
+        <v>0.4525186093365728</v>
       </c>
       <c r="D41">
-        <v>0.7228639268916983</v>
+        <v>0.7169512961198975</v>
       </c>
       <c r="E41">
-        <v>0.7199199041542396</v>
+        <v>0.7086159258801906</v>
       </c>
       <c r="F41">
-        <v>0.7352100733342646</v>
+        <v>0.7353601281865361</v>
       </c>
       <c r="G41">
-        <v>2.178380263398612</v>
+        <v>1.855404308258528</v>
       </c>
       <c r="H41">
-        <v>2.379416815148511</v>
+        <v>2.187296156634559</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-0.08881406743880016</v>
+        <v>-0.08640707393737473</v>
       </c>
       <c r="C42">
-        <v>-0.1141604528632928</v>
+        <v>-0.1131296478327803</v>
       </c>
       <c r="D42">
-        <v>-0.1807159731476945</v>
+        <v>-0.1792378115438471</v>
       </c>
       <c r="E42">
-        <v>-0.1799799583106109</v>
+        <v>-0.177153956858207</v>
       </c>
       <c r="F42">
-        <v>-0.1838022855727117</v>
+        <v>-0.1838397723872708</v>
       </c>
       <c r="G42">
-        <v>-0.4403689130879855</v>
+        <v>-0.3835210286681388</v>
       </c>
       <c r="H42">
-        <v>-0.476138417622014</v>
+        <v>-0.4423566159250902</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>4.912932321804402</v>
+        <v>4.899114044791552</v>
       </c>
       <c r="C43">
-        <v>4.859065287328693</v>
+        <v>4.875668783011225</v>
       </c>
       <c r="D43">
-        <v>5.775306888269562</v>
+        <v>5.88330700013278</v>
       </c>
       <c r="E43">
-        <v>5.824836356107772</v>
+        <v>6.303467686585651</v>
       </c>
       <c r="F43">
-        <v>3.931078297438398</v>
+        <v>5.145384769277674</v>
       </c>
       <c r="G43">
-        <v>1.73583681304663</v>
+        <v>2.630592976005981</v>
       </c>
       <c r="H43">
-        <v>2.443321371828846</v>
+        <v>2.831939785282965</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1629,25 +1629,25 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0.2981413058842138</v>
+        <v>0.3052609315311882</v>
       </c>
       <c r="C44">
-        <v>-0.7042384201764547</v>
+        <v>-0.693783647547998</v>
       </c>
       <c r="D44">
-        <v>-0.9447215080242166</v>
+        <v>-0.9082231594117761</v>
       </c>
       <c r="E44">
-        <v>-1.340971840194929</v>
+        <v>-1.279868654042837</v>
       </c>
       <c r="F44">
-        <v>-1.94193580598383</v>
+        <v>-1.859474461887131</v>
       </c>
       <c r="G44">
-        <v>-2.407788350426755</v>
+        <v>-2.418064782694952</v>
       </c>
       <c r="H44">
-        <v>-3.199734146346878</v>
+        <v>-3.208197716784164</v>
       </c>
     </row>
   </sheetData>
